--- a/docentes/Velasco Sánchez David - Estadisticos 20231.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20231.xlsx
@@ -88,34 +88,34 @@
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>SOLIS</t>
   </si>
   <si>
     <t>TIBURCIO</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>SOLANO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>RAMOS</t>
   </si>
   <si>
     <t>YAMILET MONSERRAT</t>
   </si>
   <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
     <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
   </si>
   <si>
     <t>IVANNA DANIELA</t>
@@ -646,7 +646,7 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -655,13 +655,13 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>82.86</v>
+        <v>83.33</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -826,19 +826,22 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>83.33</v>
+      </c>
+      <c r="H7">
+        <v>6.6</v>
       </c>
     </row>
   </sheetData>
@@ -1018,7 +1021,7 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -1027,13 +1030,13 @@
         <v>6</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>82.86</v>
+        <v>83.33</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -1098,7 +1101,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920321</v>
+        <v>21330051920323</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1121,7 +1124,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920323</v>
+        <v>21330051920321</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -1139,7 +1142,7 @@
         <v>15</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1162,7 +1165,7 @@
         <v>15</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Velasco Sánchez David - Estadisticos 20231.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="37">
   <si>
     <t>Mat</t>
   </si>
@@ -85,34 +85,43 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
     <t>SOLIS</t>
   </si>
   <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>TIBURCIO</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>SOLANO</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
+    <t>ABIGAIL</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
+  </si>
+  <si>
     <t>YAMILET MONSERRAT</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
   </si>
   <si>
     <t>ANA LAURA</t>
@@ -714,16 +723,19 @@
         <v>27</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>66.67</v>
+      </c>
+      <c r="H2">
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -737,16 +749,19 @@
         <v>24</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -806,16 +821,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>84</v>
+      </c>
+      <c r="H6">
+        <v>7.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -897,16 +915,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>81.48</v>
+        <v>66.67</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -923,16 +941,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>83.33</v>
+        <v>75</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1001,16 +1019,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1046,7 +1064,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1078,22 +1096,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920302</v>
+        <v>21330051920353</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1107,10 +1125,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1124,16 +1142,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920321</v>
+        <v>21330051920302</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1147,16 +1165,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920326</v>
+        <v>21330051920321</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1165,6 +1183,29 @@
         <v>15</v>
       </c>
       <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920326</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Velasco Sánchez David - Estadisticos 20231.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20231.xlsx
@@ -775,16 +775,19 @@
         <v>39</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>94.87</v>
+      </c>
+      <c r="H4">
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -798,16 +801,19 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>86.67</v>
+      </c>
+      <c r="H5">
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -993,16 +999,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G5">
-        <v>83.33</v>
+        <v>86.67</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">

--- a/docentes/Velasco Sánchez David - Estadisticos 20231.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -88,46 +88,10 @@
     <t>VILLEGAS</t>
   </si>
   <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
     <t>CORONA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
-  </si>
-  <si>
-    <t>YAMILET MONSERRAT</t>
-  </si>
-  <si>
-    <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>IVANNA DANIELA</t>
   </si>
 </sst>
 </file>
@@ -664,13 +628,13 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>83.33</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -856,16 +820,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>83.33</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>6.6</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
@@ -1051,16 +1015,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G7">
-        <v>83.33</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -1070,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1108,10 +1072,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1121,98 +1085,6 @@
       </c>
       <c r="G2">
         <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920323</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920302</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920321</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920326</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Velasco Sánchez David - Estadisticos 20231.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,15 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
   </si>
 </sst>
 </file>
@@ -885,16 +876,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>66.67</v>
+        <v>85.19</v>
       </c>
       <c r="H2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -911,13 +902,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>75</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
         <v>7.5</v>
@@ -937,16 +928,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G4">
-        <v>94.87</v>
+        <v>92.31</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -963,16 +954,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G5">
-        <v>86.67</v>
+        <v>96.67</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -989,13 +980,13 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="H6">
         <v>8</v>
@@ -1024,7 +1015,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -1034,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1064,29 +1055,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920353</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Velasco Sánchez David - Estadisticos 20231.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20231.xlsx
@@ -885,7 +885,7 @@
         <v>85.19</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -911,7 +911,7 @@
         <v>83.33</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -937,7 +937,7 @@
         <v>92.31</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -963,7 +963,7 @@
         <v>96.67</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -989,7 +989,7 @@
         <v>96</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1015,7 +1015,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Velasco Sánchez David - Estadisticos 20231.xlsx
+++ b/docentes/Velasco Sánchez David - Estadisticos 20231.xlsx
@@ -885,7 +885,7 @@
         <v>85.19</v>
       </c>
       <c r="H2">
-        <v>9.300000000000001</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -911,7 +911,7 @@
         <v>83.33</v>
       </c>
       <c r="H3">
-        <v>9.199999999999999</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -937,7 +937,7 @@
         <v>92.31</v>
       </c>
       <c r="H4">
-        <v>9.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -963,7 +963,7 @@
         <v>96.67</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -989,7 +989,7 @@
         <v>96</v>
       </c>
       <c r="H6">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1015,7 +1015,7 @@
         <v>100</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
